--- a/backend/wp_templates/H/H2 在建工程.xlsx
+++ b/backend/wp_templates/H/H2 在建工程.xlsx
@@ -32317,58 +32317,6 @@
   </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-  <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject shapeId="3073" progId="Equation.3" r:id="rId3">
-          <objectPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>99060</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject shapeId="3073" progId="Equation.3" r:id="rId3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject shapeId="3074" progId="Equation.3" r:id="rId5">
-          <objectPr defaultSize="0" r:id="rId6">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>655320</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>144780</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>198120</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject shapeId="3074" progId="Equation.3" r:id="rId5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </oleObjects>
 </worksheet>
 </file>
 

--- a/backend/wp_templates/H/H2 在建工程.xlsx
+++ b/backend/wp_templates/H/H2 在建工程.xlsx
@@ -42235,7 +42235,7 @@
       <c r="B13" s="520"/>
       <c r="C13" s="475"/>
       <c r="D13" s="521">
-        <f>IF(AH13=0,0,AH13/B13)</f>
+        <f>IF(B13=0,0,AG13/B13)</f>
         <v>0</v>
       </c>
       <c r="E13" s="383"/>
@@ -42336,11 +42336,11 @@
         <v>0</v>
       </c>
       <c r="AV13" s="248">
-        <f>R13-AL13</f>
+        <f>Q13-AL13</f>
         <v>0</v>
       </c>
       <c r="AW13" s="248">
-        <f>AH13-AS13</f>
+        <f>AG13-AS13</f>
         <v>0</v>
       </c>
       <c r="AX13" s="475"/>
@@ -42350,7 +42350,7 @@
       <c r="B14" s="520"/>
       <c r="C14" s="475"/>
       <c r="D14" s="521">
-        <f t="shared" ref="D14:D20" si="1">IF(AH14=0,0,AH14/B14)</f>
+        <f t="shared" ref="D14:D20" si="1">IF(B14=0,0,AG14/B14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="383"/>
@@ -42451,11 +42451,11 @@
         <v>0</v>
       </c>
       <c r="AV14" s="248">
-        <f t="shared" ref="AV14:AV20" si="17">R14-AL14</f>
+        <f t="shared" ref="AV14:AV20" si="17">Q14-AL14</f>
         <v>0</v>
       </c>
       <c r="AW14" s="248">
-        <f t="shared" ref="AW14:AW20" si="18">AH14-AS14</f>
+        <f t="shared" ref="AW14:AW20" si="18">AG14-AS14</f>
         <v>0</v>
       </c>
       <c r="AX14" s="475"/>
